--- a/artfynd/A 14246-2021 artfynd.xlsx
+++ b/artfynd/A 14246-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 14246-2021 artfynd.xlsx
+++ b/artfynd/A 14246-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74302508</v>
       </c>
       <c r="B2" t="n">
-        <v>96309</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98563</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547474.8253373385</v>
+        <v>547475</v>
       </c>
       <c r="R2" t="n">
-        <v>6350715.135372299</v>
+        <v>6350715</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1986-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1986-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -804,12 +789,7 @@
         <v>75016378</v>
       </c>
       <c r="B3" t="n">
-        <v>101120</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103106</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>547574.9655770997</v>
+        <v>547575</v>
       </c>
       <c r="R3" t="n">
-        <v>6350716.835647012</v>
+        <v>6350717</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -874,19 +854,9 @@
           <t>1986-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1989-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 14246-2021 artfynd.xlsx
+++ b/artfynd/A 14246-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74302508</v>
       </c>
       <c r="B2" t="n">
-        <v>98563</v>
+        <v>98566</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>75016378</v>
       </c>
       <c r="B3" t="n">
-        <v>103106</v>
+        <v>103112</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14246-2021 artfynd.xlsx
+++ b/artfynd/A 14246-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74302508</v>
       </c>
       <c r="B2" t="n">
-        <v>98566</v>
+        <v>98567</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>75016378</v>
       </c>
       <c r="B3" t="n">
-        <v>103112</v>
+        <v>103114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14246-2021 artfynd.xlsx
+++ b/artfynd/A 14246-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74302508</v>
       </c>
       <c r="B2" t="n">
-        <v>98567</v>
+        <v>98594</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>75016378</v>
       </c>
       <c r="B3" t="n">
-        <v>103114</v>
+        <v>103141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14246-2021 artfynd.xlsx
+++ b/artfynd/A 14246-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74302508</v>
       </c>
       <c r="B2" t="n">
-        <v>98594</v>
+        <v>98600</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>75016378</v>
       </c>
       <c r="B3" t="n">
-        <v>103141</v>
+        <v>103147</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14246-2021 artfynd.xlsx
+++ b/artfynd/A 14246-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74302508</v>
       </c>
       <c r="B2" t="n">
-        <v>98600</v>
+        <v>98607</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>75016378</v>
       </c>
       <c r="B3" t="n">
-        <v>103147</v>
+        <v>103154</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14246-2021 artfynd.xlsx
+++ b/artfynd/A 14246-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74302508</v>
       </c>
       <c r="B2" t="n">
-        <v>98607</v>
+        <v>98611</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>75016378</v>
       </c>
       <c r="B3" t="n">
-        <v>103154</v>
+        <v>103158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14246-2021 artfynd.xlsx
+++ b/artfynd/A 14246-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74302508</v>
       </c>
       <c r="B2" t="n">
-        <v>98611</v>
+        <v>98618</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>75016378</v>
       </c>
       <c r="B3" t="n">
-        <v>103158</v>
+        <v>103165</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14246-2021 artfynd.xlsx
+++ b/artfynd/A 14246-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74302508</v>
       </c>
       <c r="B2" t="n">
-        <v>98621</v>
+        <v>98626</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>75016378</v>
       </c>
       <c r="B3" t="n">
-        <v>103168</v>
+        <v>103173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14246-2021 artfynd.xlsx
+++ b/artfynd/A 14246-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74302508</v>
       </c>
       <c r="B2" t="n">
-        <v>98626</v>
+        <v>98634</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>75016378</v>
       </c>
       <c r="B3" t="n">
-        <v>103173</v>
+        <v>103181</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14246-2021 artfynd.xlsx
+++ b/artfynd/A 14246-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74302508</v>
       </c>
       <c r="B2" t="n">
-        <v>98634</v>
+        <v>98644</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>75016378</v>
       </c>
       <c r="B3" t="n">
-        <v>103181</v>
+        <v>103191</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
